--- a/output/yearly_population_iteration_87_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_87_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5629</v>
+        <v>8936</v>
       </c>
       <c r="C2" t="n">
-        <v>6166</v>
+        <v>4165</v>
       </c>
       <c r="D2" t="n">
-        <v>19503</v>
+        <v>25004</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3181</v>
+        <v>4762</v>
       </c>
       <c r="C3" t="n">
-        <v>3875</v>
+        <v>2964</v>
       </c>
       <c r="D3" t="n">
-        <v>12817</v>
+        <v>17150</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2640</v>
+        <v>3657</v>
       </c>
       <c r="C4" t="n">
-        <v>3947</v>
+        <v>3342</v>
       </c>
       <c r="D4" t="n">
-        <v>6719</v>
+        <v>9026</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1840</v>
+        <v>2467</v>
       </c>
       <c r="C5" t="n">
-        <v>3098</v>
+        <v>3188</v>
       </c>
       <c r="D5" t="n">
-        <v>2622</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1136</v>
+        <v>1428</v>
       </c>
       <c r="C6" t="n">
-        <v>2456</v>
+        <v>2219</v>
       </c>
       <c r="D6" t="n">
-        <v>1168</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>551</v>
+        <v>690</v>
       </c>
       <c r="C7" t="n">
-        <v>1687</v>
+        <v>1139</v>
       </c>
       <c r="D7" t="n">
-        <v>651</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="C8" t="n">
-        <v>842</v>
+        <v>486</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>369</v>
+        <v>264</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7037</v>
+        <v>10098</v>
       </c>
       <c r="C2" t="n">
-        <v>9530</v>
+        <v>5388</v>
       </c>
       <c r="D2" t="n">
-        <v>30985</v>
+        <v>23491</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3481</v>
+        <v>5386</v>
       </c>
       <c r="C3" t="n">
-        <v>4350</v>
+        <v>3093</v>
       </c>
       <c r="D3" t="n">
-        <v>12897</v>
+        <v>17065</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2469</v>
+        <v>3582</v>
       </c>
       <c r="C4" t="n">
-        <v>3828</v>
+        <v>3055</v>
       </c>
       <c r="D4" t="n">
-        <v>7568</v>
+        <v>9990</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1947</v>
+        <v>2645</v>
       </c>
       <c r="C5" t="n">
-        <v>3411</v>
+        <v>3195</v>
       </c>
       <c r="D5" t="n">
-        <v>3185</v>
+        <v>4061</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1337</v>
+        <v>1716</v>
       </c>
       <c r="C6" t="n">
-        <v>2732</v>
+        <v>2621</v>
       </c>
       <c r="D6" t="n">
-        <v>1389</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>725</v>
+        <v>916</v>
       </c>
       <c r="C7" t="n">
-        <v>2023</v>
+        <v>1635</v>
       </c>
       <c r="D7" t="n">
-        <v>725</v>
+        <v>749</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>315</v>
+        <v>384</v>
       </c>
       <c r="C8" t="n">
-        <v>1222</v>
+        <v>769</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="C9" t="n">
-        <v>569</v>
+        <v>359</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>280</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
         <v>160</v>
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10882</v>
+        <v>12899</v>
       </c>
       <c r="C2" t="n">
-        <v>9302</v>
+        <v>6664</v>
       </c>
       <c r="D2" t="n">
-        <v>30698</v>
+        <v>32561</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4031</v>
+        <v>5949</v>
       </c>
       <c r="C3" t="n">
-        <v>5831</v>
+        <v>3599</v>
       </c>
       <c r="D3" t="n">
-        <v>14366</v>
+        <v>16768</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2490</v>
+        <v>3681</v>
       </c>
       <c r="C4" t="n">
-        <v>3988</v>
+        <v>2979</v>
       </c>
       <c r="D4" t="n">
-        <v>8083</v>
+        <v>10677</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1932</v>
+        <v>2699</v>
       </c>
       <c r="C5" t="n">
-        <v>3491</v>
+        <v>3066</v>
       </c>
       <c r="D5" t="n">
-        <v>3761</v>
+        <v>4848</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1456</v>
+        <v>1919</v>
       </c>
       <c r="C6" t="n">
-        <v>2999</v>
+        <v>2813</v>
       </c>
       <c r="D6" t="n">
-        <v>1615</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>880</v>
+        <v>1129</v>
       </c>
       <c r="C7" t="n">
-        <v>2301</v>
+        <v>2033</v>
       </c>
       <c r="D7" t="n">
-        <v>815</v>
+        <v>854</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>429</v>
+        <v>525</v>
       </c>
       <c r="C8" t="n">
-        <v>1539</v>
+        <v>1125</v>
       </c>
       <c r="D8" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="C9" t="n">
-        <v>831</v>
+        <v>516</v>
       </c>
       <c r="D9" t="n">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C10" t="n">
-        <v>387</v>
+        <v>277</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9540</v>
+        <v>11551</v>
       </c>
       <c r="C2" t="n">
-        <v>6176</v>
+        <v>4424</v>
       </c>
       <c r="D2" t="n">
-        <v>24864</v>
+        <v>26432</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4731</v>
+        <v>6988</v>
       </c>
       <c r="C3" t="n">
-        <v>8394</v>
+        <v>5533</v>
       </c>
       <c r="D3" t="n">
-        <v>15890</v>
+        <v>18891</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1785</v>
+        <v>2493</v>
       </c>
       <c r="C4" t="n">
-        <v>5648</v>
+        <v>4630</v>
       </c>
       <c r="D4" t="n">
-        <v>7917</v>
+        <v>10376</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1345</v>
+        <v>1773</v>
       </c>
       <c r="C5" t="n">
-        <v>2939</v>
+        <v>2756</v>
       </c>
       <c r="D5" t="n">
-        <v>2629</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>813</v>
+        <v>1043</v>
       </c>
       <c r="C6" t="n">
-        <v>2254</v>
+        <v>1992</v>
       </c>
       <c r="D6" t="n">
-        <v>798</v>
+        <v>836</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>396</v>
+        <v>485</v>
       </c>
       <c r="C7" t="n">
-        <v>1508</v>
+        <v>1102</v>
       </c>
       <c r="D7" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="C8" t="n">
-        <v>814</v>
+        <v>505</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>379</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5589</v>
+        <v>6829</v>
       </c>
       <c r="C2" t="n">
-        <v>2736</v>
+        <v>2257</v>
       </c>
       <c r="D2" t="n">
-        <v>17742</v>
+        <v>18403</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5785</v>
+        <v>7691</v>
       </c>
       <c r="C3" t="n">
-        <v>6647</v>
+        <v>4531</v>
       </c>
       <c r="D3" t="n">
-        <v>16394</v>
+        <v>19039</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2576</v>
+        <v>3715</v>
       </c>
       <c r="C4" t="n">
-        <v>7011</v>
+        <v>5144</v>
       </c>
       <c r="D4" t="n">
-        <v>8976</v>
+        <v>11468</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1451</v>
+        <v>1944</v>
       </c>
       <c r="C5" t="n">
-        <v>4189</v>
+        <v>3596</v>
       </c>
       <c r="D5" t="n">
-        <v>3335</v>
+        <v>4127</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>974</v>
+        <v>1254</v>
       </c>
       <c r="C6" t="n">
-        <v>2640</v>
+        <v>2391</v>
       </c>
       <c r="D6" t="n">
-        <v>987</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>374</v>
+        <v>458</v>
       </c>
       <c r="C7" t="n">
-        <v>1852</v>
+        <v>1451</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="C8" t="n">
-        <v>1046</v>
+        <v>680</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>445</v>
+        <v>324</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5669</v>
+        <v>7837</v>
       </c>
       <c r="C2" t="n">
-        <v>5087</v>
+        <v>5637</v>
       </c>
       <c r="D2" t="n">
-        <v>14307</v>
+        <v>30432</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4776</v>
+        <v>6138</v>
       </c>
       <c r="C3" t="n">
-        <v>4181</v>
+        <v>3019</v>
       </c>
       <c r="D3" t="n">
-        <v>15460</v>
+        <v>17637</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3436</v>
+        <v>4685</v>
       </c>
       <c r="C4" t="n">
-        <v>6679</v>
+        <v>4725</v>
       </c>
       <c r="D4" t="n">
-        <v>9984</v>
+        <v>12427</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1722</v>
+        <v>2429</v>
       </c>
       <c r="C5" t="n">
-        <v>5523</v>
+        <v>4279</v>
       </c>
       <c r="D5" t="n">
-        <v>4154</v>
+        <v>5199</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1090</v>
+        <v>1429</v>
       </c>
       <c r="C6" t="n">
-        <v>3327</v>
+        <v>2956</v>
       </c>
       <c r="D6" t="n">
-        <v>1334</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>547</v>
+        <v>690</v>
       </c>
       <c r="C7" t="n">
-        <v>2224</v>
+        <v>1888</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="C8" t="n">
-        <v>1395</v>
+        <v>1011</v>
       </c>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>684</v>
+        <v>466</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>314</v>
+        <v>259</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
         <v>168</v>
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3293</v>
+        <v>4569</v>
       </c>
       <c r="C2" t="n">
-        <v>2314</v>
+        <v>2537</v>
       </c>
       <c r="D2" t="n">
-        <v>9882</v>
+        <v>20992</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4864</v>
+        <v>6388</v>
       </c>
       <c r="C3" t="n">
-        <v>4359</v>
+        <v>3839</v>
       </c>
       <c r="D3" t="n">
-        <v>14959</v>
+        <v>18646</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3824</v>
+        <v>5180</v>
       </c>
       <c r="C4" t="n">
-        <v>6317</v>
+        <v>4490</v>
       </c>
       <c r="D4" t="n">
-        <v>10685</v>
+        <v>13145</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1848</v>
+        <v>2553</v>
       </c>
       <c r="C5" t="n">
-        <v>6514</v>
+        <v>4954</v>
       </c>
       <c r="D5" t="n">
-        <v>4501</v>
+        <v>5617</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>968</v>
+        <v>1244</v>
       </c>
       <c r="C6" t="n">
-        <v>4240</v>
+        <v>3693</v>
       </c>
       <c r="D6" t="n">
-        <v>1313</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C7" t="n">
-        <v>2441</v>
+        <v>1958</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>1121</v>
+        <v>783</v>
       </c>
       <c r="D8" t="n">
         <v>385</v>
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>253</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
         <v>164</v>
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4772</v>
+        <v>5603</v>
       </c>
       <c r="C2" t="n">
-        <v>7064</v>
+        <v>2154</v>
       </c>
       <c r="D2" t="n">
-        <v>9161</v>
+        <v>19777</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3577</v>
+        <v>4782</v>
       </c>
       <c r="C3" t="n">
-        <v>2971</v>
+        <v>2861</v>
       </c>
       <c r="D3" t="n">
-        <v>13342</v>
+        <v>17879</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3719</v>
+        <v>5011</v>
       </c>
       <c r="C4" t="n">
-        <v>5268</v>
+        <v>4077</v>
       </c>
       <c r="D4" t="n">
-        <v>11057</v>
+        <v>13643</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2382</v>
+        <v>3213</v>
       </c>
       <c r="C5" t="n">
-        <v>6348</v>
+        <v>4680</v>
       </c>
       <c r="D5" t="n">
-        <v>5314</v>
+        <v>6602</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1198</v>
+        <v>1594</v>
       </c>
       <c r="C6" t="n">
-        <v>5245</v>
+        <v>4250</v>
       </c>
       <c r="D6" t="n">
-        <v>1754</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>384</v>
+        <v>484</v>
       </c>
       <c r="C7" t="n">
-        <v>3245</v>
+        <v>2726</v>
       </c>
       <c r="D7" t="n">
-        <v>685</v>
+        <v>705</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>1647</v>
+        <v>1247</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>595</v>
+        <v>442</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
         <v>175</v>
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
         <v>100</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3246</v>
+        <v>4302</v>
       </c>
       <c r="C2" t="n">
-        <v>3844</v>
+        <v>1489</v>
       </c>
       <c r="D2" t="n">
-        <v>6441</v>
+        <v>15221</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3484</v>
+        <v>4428</v>
       </c>
       <c r="C3" t="n">
-        <v>4224</v>
+        <v>2320</v>
       </c>
       <c r="D3" t="n">
-        <v>12187</v>
+        <v>17292</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3383</v>
+        <v>4548</v>
       </c>
       <c r="C4" t="n">
-        <v>4317</v>
+        <v>3584</v>
       </c>
       <c r="D4" t="n">
-        <v>11134</v>
+        <v>13928</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2631</v>
+        <v>3548</v>
       </c>
       <c r="C5" t="n">
-        <v>6045</v>
+        <v>4530</v>
       </c>
       <c r="D5" t="n">
-        <v>5865</v>
+        <v>7275</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1436</v>
+        <v>1915</v>
       </c>
       <c r="C6" t="n">
-        <v>5824</v>
+        <v>4568</v>
       </c>
       <c r="D6" t="n">
-        <v>2125</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>374</v>
+        <v>472</v>
       </c>
       <c r="C7" t="n">
-        <v>3995</v>
+        <v>3315</v>
       </c>
       <c r="D7" t="n">
-        <v>769</v>
+        <v>807</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>2090</v>
+        <v>1630</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>723</v>
+        <v>546</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
         <v>180</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
         <v>137</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5817</v>
+        <v>6361</v>
       </c>
       <c r="C2" t="n">
-        <v>11107</v>
+        <v>10939</v>
       </c>
       <c r="D2" t="n">
-        <v>9626</v>
+        <v>15040</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2853</v>
+        <v>3681</v>
       </c>
       <c r="C3" t="n">
-        <v>3635</v>
+        <v>1740</v>
       </c>
       <c r="D3" t="n">
-        <v>10652</v>
+        <v>15892</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3001</v>
+        <v>3913</v>
       </c>
       <c r="C4" t="n">
-        <v>4144</v>
+        <v>2939</v>
       </c>
       <c r="D4" t="n">
-        <v>10957</v>
+        <v>14021</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2637</v>
+        <v>3591</v>
       </c>
       <c r="C5" t="n">
-        <v>5230</v>
+        <v>4027</v>
       </c>
       <c r="D5" t="n">
-        <v>6445</v>
+        <v>8011</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1731</v>
+        <v>2320</v>
       </c>
       <c r="C6" t="n">
-        <v>5861</v>
+        <v>4511</v>
       </c>
       <c r="D6" t="n">
-        <v>2600</v>
+        <v>3148</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>650</v>
+        <v>849</v>
       </c>
       <c r="C7" t="n">
-        <v>4710</v>
+        <v>3849</v>
       </c>
       <c r="D7" t="n">
-        <v>933</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="C8" t="n">
-        <v>2819</v>
+        <v>2256</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>1198</v>
+        <v>933</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>393</v>
+        <v>329</v>
       </c>
       <c r="D10" t="n">
         <v>189</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
         <v>140</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
         <v>95</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6546</v>
+        <v>9425</v>
       </c>
       <c r="C2" t="n">
-        <v>6587</v>
+        <v>3030</v>
       </c>
       <c r="D2" t="n">
-        <v>9828</v>
+        <v>12421</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4067</v>
+        <v>4458</v>
       </c>
       <c r="C2" t="n">
-        <v>6131</v>
+        <v>6038</v>
       </c>
       <c r="D2" t="n">
-        <v>7084</v>
+        <v>10950</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3956</v>
+        <v>4964</v>
       </c>
       <c r="C3" t="n">
-        <v>5790</v>
+        <v>4166</v>
       </c>
       <c r="D3" t="n">
-        <v>11473</v>
+        <v>17146</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3951</v>
+        <v>5319</v>
       </c>
       <c r="C4" t="n">
-        <v>5938</v>
+        <v>4198</v>
       </c>
       <c r="D4" t="n">
-        <v>11372</v>
+        <v>14498</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1721</v>
+        <v>2309</v>
       </c>
       <c r="C5" t="n">
-        <v>7994</v>
+        <v>6110</v>
       </c>
       <c r="D5" t="n">
-        <v>5950</v>
+        <v>7356</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>600</v>
+        <v>784</v>
       </c>
       <c r="C6" t="n">
-        <v>5879</v>
+        <v>4788</v>
       </c>
       <c r="D6" t="n">
-        <v>2085</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>2762</v>
+        <v>2210</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1174</v>
+        <v>914</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>385</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
         <v>185</v>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D10" t="n">
         <v>137</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
         <v>93</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7640</v>
+        <v>8330</v>
       </c>
       <c r="C2" t="n">
-        <v>5512</v>
+        <v>2391</v>
       </c>
       <c r="D2" t="n">
-        <v>19509</v>
+        <v>17264</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2781</v>
+        <v>4001</v>
       </c>
       <c r="C3" t="n">
-        <v>3319</v>
+        <v>1527</v>
       </c>
       <c r="D3" t="n">
-        <v>2290</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="4">
@@ -4554,7 +4554,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
         <v>381</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5135</v>
+        <v>6343</v>
       </c>
       <c r="C2" t="n">
-        <v>6348</v>
+        <v>5696</v>
       </c>
       <c r="D2" t="n">
-        <v>16504</v>
+        <v>21591</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4278</v>
+        <v>5068</v>
       </c>
       <c r="C3" t="n">
-        <v>3932</v>
+        <v>1738</v>
       </c>
       <c r="D3" t="n">
-        <v>5014</v>
+        <v>4967</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1242</v>
+        <v>1772</v>
       </c>
       <c r="C4" t="n">
-        <v>1989</v>
+        <v>939</v>
       </c>
       <c r="D4" t="n">
-        <v>1642</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4885,7 +4885,7 @@
         <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>870</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5461</v>
+        <v>7653</v>
       </c>
       <c r="C2" t="n">
-        <v>4089</v>
+        <v>7218</v>
       </c>
       <c r="D2" t="n">
-        <v>18280</v>
+        <v>33994</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3871</v>
+        <v>4688</v>
       </c>
       <c r="C3" t="n">
-        <v>4543</v>
+        <v>3372</v>
       </c>
       <c r="D3" t="n">
-        <v>6491</v>
+        <v>7269</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2346</v>
+        <v>2900</v>
       </c>
       <c r="C4" t="n">
-        <v>3048</v>
+        <v>1372</v>
       </c>
       <c r="D4" t="n">
-        <v>2239</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>559</v>
+        <v>787</v>
       </c>
       <c r="C5" t="n">
-        <v>1182</v>
+        <v>609</v>
       </c>
       <c r="D5" t="n">
-        <v>1231</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5387</v>
+        <v>7256</v>
       </c>
       <c r="C2" t="n">
-        <v>3759</v>
+        <v>4511</v>
       </c>
       <c r="D2" t="n">
-        <v>21162</v>
+        <v>36075</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3801</v>
+        <v>4994</v>
       </c>
       <c r="C3" t="n">
-        <v>3750</v>
+        <v>4657</v>
       </c>
       <c r="D3" t="n">
-        <v>7825</v>
+        <v>10819</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2649</v>
+        <v>3236</v>
       </c>
       <c r="C4" t="n">
-        <v>3759</v>
+        <v>2418</v>
       </c>
       <c r="D4" t="n">
-        <v>2946</v>
+        <v>3134</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1188</v>
+        <v>1519</v>
       </c>
       <c r="C5" t="n">
-        <v>2142</v>
+        <v>986</v>
       </c>
       <c r="D5" t="n">
-        <v>1355</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>306</v>
+        <v>398</v>
       </c>
       <c r="C6" t="n">
-        <v>745</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>958</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -5574,7 +5574,7 @@
         <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5591,7 +5591,7 @@
         <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5776</v>
+        <v>8298</v>
       </c>
       <c r="C2" t="n">
-        <v>5855</v>
+        <v>5250</v>
       </c>
       <c r="D2" t="n">
-        <v>29423</v>
+        <v>35532</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3327</v>
+        <v>4432</v>
       </c>
       <c r="C3" t="n">
-        <v>3075</v>
+        <v>3754</v>
       </c>
       <c r="D3" t="n">
-        <v>8750</v>
+        <v>13073</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1989</v>
+        <v>2536</v>
       </c>
       <c r="C4" t="n">
-        <v>3046</v>
+        <v>2973</v>
       </c>
       <c r="D4" t="n">
-        <v>3243</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1000</v>
+        <v>1251</v>
       </c>
       <c r="C5" t="n">
-        <v>2190</v>
+        <v>1276</v>
       </c>
       <c r="D5" t="n">
-        <v>1300</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>356</v>
+        <v>449</v>
       </c>
       <c r="C6" t="n">
-        <v>971</v>
+        <v>486</v>
       </c>
       <c r="D6" t="n">
-        <v>773</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>256</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>194</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5916,7 +5916,7 @@
         <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4749</v>
+        <v>6928</v>
       </c>
       <c r="C2" t="n">
-        <v>5979</v>
+        <v>3668</v>
       </c>
       <c r="D2" t="n">
-        <v>23984</v>
+        <v>29678</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3781</v>
+        <v>5293</v>
       </c>
       <c r="C3" t="n">
-        <v>4060</v>
+        <v>3985</v>
       </c>
       <c r="D3" t="n">
-        <v>11730</v>
+        <v>16042</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2315</v>
+        <v>3060</v>
       </c>
       <c r="C4" t="n">
-        <v>3000</v>
+        <v>3391</v>
       </c>
       <c r="D4" t="n">
-        <v>4307</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1343</v>
+        <v>1679</v>
       </c>
       <c r="C5" t="n">
-        <v>2653</v>
+        <v>2259</v>
       </c>
       <c r="D5" t="n">
-        <v>1652</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>633</v>
+        <v>793</v>
       </c>
       <c r="C6" t="n">
-        <v>1661</v>
+        <v>935</v>
       </c>
       <c r="D6" t="n">
-        <v>855</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>205</v>
+        <v>256</v>
       </c>
       <c r="C7" t="n">
-        <v>703</v>
+        <v>386</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>293</v>
+        <v>241</v>
       </c>
       <c r="D8" t="n">
         <v>386</v>
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4247</v>
+        <v>6602</v>
       </c>
       <c r="C2" t="n">
-        <v>4476</v>
+        <v>3498</v>
       </c>
       <c r="D2" t="n">
-        <v>18608</v>
+        <v>25513</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3510</v>
+        <v>5071</v>
       </c>
       <c r="C3" t="n">
-        <v>4428</v>
+        <v>3299</v>
       </c>
       <c r="D3" t="n">
-        <v>12846</v>
+        <v>17068</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2636</v>
+        <v>3565</v>
       </c>
       <c r="C4" t="n">
-        <v>3548</v>
+        <v>3624</v>
       </c>
       <c r="D4" t="n">
-        <v>5559</v>
+        <v>7512</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1604</v>
+        <v>2089</v>
       </c>
       <c r="C5" t="n">
-        <v>2791</v>
+        <v>2842</v>
       </c>
       <c r="D5" t="n">
-        <v>2111</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>904</v>
+        <v>1116</v>
       </c>
       <c r="C6" t="n">
-        <v>2158</v>
+        <v>1635</v>
       </c>
       <c r="D6" t="n">
-        <v>988</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>369</v>
+        <v>464</v>
       </c>
       <c r="C7" t="n">
-        <v>1219</v>
+        <v>676</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="C8" t="n">
-        <v>505</v>
+        <v>312</v>
       </c>
       <c r="D8" t="n">
         <v>412</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>155</v>
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_87_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_87_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8936</v>
+        <v>8254</v>
       </c>
       <c r="C2" t="n">
-        <v>4165</v>
+        <v>7015</v>
       </c>
       <c r="D2" t="n">
-        <v>25004</v>
+        <v>38903</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4762</v>
+        <v>4386</v>
       </c>
       <c r="C3" t="n">
-        <v>2964</v>
+        <v>4563</v>
       </c>
       <c r="D3" t="n">
-        <v>17150</v>
+        <v>17086</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3657</v>
+        <v>3202</v>
       </c>
       <c r="C4" t="n">
-        <v>3342</v>
+        <v>5534</v>
       </c>
       <c r="D4" t="n">
-        <v>9026</v>
+        <v>8811</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2467</v>
+        <v>1977</v>
       </c>
       <c r="C5" t="n">
-        <v>3188</v>
+        <v>4023</v>
       </c>
       <c r="D5" t="n">
-        <v>3210</v>
+        <v>3337</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1428</v>
+        <v>1047</v>
       </c>
       <c r="C6" t="n">
-        <v>2219</v>
+        <v>2628</v>
       </c>
       <c r="D6" t="n">
-        <v>1249</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>690</v>
+        <v>459</v>
       </c>
       <c r="C7" t="n">
-        <v>1139</v>
+        <v>1428</v>
       </c>
       <c r="D7" t="n">
-        <v>665</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>252</v>
+        <v>177</v>
       </c>
       <c r="C8" t="n">
-        <v>486</v>
+        <v>614</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
         <v>309</v>
@@ -895,7 +895,7 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
         <v>243</v>
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -948,7 +948,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>76</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10098</v>
+        <v>7985</v>
       </c>
       <c r="C2" t="n">
-        <v>5388</v>
+        <v>4939</v>
       </c>
       <c r="D2" t="n">
-        <v>23491</v>
+        <v>47517</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5386</v>
+        <v>4940</v>
       </c>
       <c r="C3" t="n">
-        <v>3093</v>
+        <v>4996</v>
       </c>
       <c r="D3" t="n">
-        <v>17065</v>
+        <v>18904</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3582</v>
+        <v>3206</v>
       </c>
       <c r="C4" t="n">
-        <v>3055</v>
+        <v>4952</v>
       </c>
       <c r="D4" t="n">
-        <v>9990</v>
+        <v>9893</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2645</v>
+        <v>2205</v>
       </c>
       <c r="C5" t="n">
-        <v>3195</v>
+        <v>4596</v>
       </c>
       <c r="D5" t="n">
-        <v>4061</v>
+        <v>4044</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1716</v>
+        <v>1312</v>
       </c>
       <c r="C6" t="n">
-        <v>2621</v>
+        <v>3231</v>
       </c>
       <c r="D6" t="n">
-        <v>1521</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>916</v>
+        <v>639</v>
       </c>
       <c r="C7" t="n">
-        <v>1635</v>
+        <v>1942</v>
       </c>
       <c r="D7" t="n">
-        <v>749</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>384</v>
+        <v>258</v>
       </c>
       <c r="C8" t="n">
-        <v>769</v>
+        <v>964</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>359</v>
+        <v>418</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12899</v>
+        <v>8827</v>
       </c>
       <c r="C2" t="n">
-        <v>6664</v>
+        <v>7327</v>
       </c>
       <c r="D2" t="n">
-        <v>32561</v>
+        <v>46954</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5949</v>
+        <v>5036</v>
       </c>
       <c r="C3" t="n">
-        <v>3599</v>
+        <v>4415</v>
       </c>
       <c r="D3" t="n">
-        <v>16768</v>
+        <v>21127</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3681</v>
+        <v>3320</v>
       </c>
       <c r="C4" t="n">
-        <v>2979</v>
+        <v>4820</v>
       </c>
       <c r="D4" t="n">
-        <v>10677</v>
+        <v>10794</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2699</v>
+        <v>2334</v>
       </c>
       <c r="C5" t="n">
-        <v>3066</v>
+        <v>4606</v>
       </c>
       <c r="D5" t="n">
-        <v>4848</v>
+        <v>4724</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1919</v>
+        <v>1513</v>
       </c>
       <c r="C6" t="n">
-        <v>2813</v>
+        <v>3765</v>
       </c>
       <c r="D6" t="n">
-        <v>1851</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1129</v>
+        <v>807</v>
       </c>
       <c r="C7" t="n">
-        <v>2033</v>
+        <v>2440</v>
       </c>
       <c r="D7" t="n">
-        <v>854</v>
+        <v>867</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>525</v>
+        <v>356</v>
       </c>
       <c r="C8" t="n">
-        <v>1125</v>
+        <v>1337</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>201</v>
+        <v>138</v>
       </c>
       <c r="C9" t="n">
-        <v>516</v>
+        <v>626</v>
       </c>
       <c r="D9" t="n">
-        <v>339</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D11" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11551</v>
+        <v>8187</v>
       </c>
       <c r="C2" t="n">
-        <v>4424</v>
+        <v>4982</v>
       </c>
       <c r="D2" t="n">
-        <v>26432</v>
+        <v>38577</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6988</v>
+        <v>6003</v>
       </c>
       <c r="C3" t="n">
-        <v>5533</v>
+        <v>7107</v>
       </c>
       <c r="D3" t="n">
-        <v>18891</v>
+        <v>22583</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2493</v>
+        <v>2156</v>
       </c>
       <c r="C4" t="n">
-        <v>4630</v>
+        <v>7059</v>
       </c>
       <c r="D4" t="n">
-        <v>10376</v>
+        <v>10311</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1773</v>
+        <v>1398</v>
       </c>
       <c r="C5" t="n">
-        <v>2756</v>
+        <v>3689</v>
       </c>
       <c r="D5" t="n">
-        <v>3163</v>
+        <v>3171</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1043</v>
+        <v>745</v>
       </c>
       <c r="C6" t="n">
-        <v>1992</v>
+        <v>2391</v>
       </c>
       <c r="D6" t="n">
-        <v>836</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>485</v>
+        <v>328</v>
       </c>
       <c r="C7" t="n">
-        <v>1102</v>
+        <v>1310</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>185</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>505</v>
+        <v>613</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6829</v>
+        <v>4915</v>
       </c>
       <c r="C2" t="n">
-        <v>2257</v>
+        <v>2705</v>
       </c>
       <c r="D2" t="n">
-        <v>18403</v>
+        <v>27205</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7691</v>
+        <v>5995</v>
       </c>
       <c r="C3" t="n">
-        <v>4531</v>
+        <v>5620</v>
       </c>
       <c r="D3" t="n">
-        <v>19039</v>
+        <v>23457</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3715</v>
+        <v>3116</v>
       </c>
       <c r="C4" t="n">
-        <v>5144</v>
+        <v>7137</v>
       </c>
       <c r="D4" t="n">
-        <v>11468</v>
+        <v>12080</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1944</v>
+        <v>1583</v>
       </c>
       <c r="C5" t="n">
-        <v>3596</v>
+        <v>5180</v>
       </c>
       <c r="D5" t="n">
-        <v>4127</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1254</v>
+        <v>889</v>
       </c>
       <c r="C6" t="n">
-        <v>2391</v>
+        <v>2962</v>
       </c>
       <c r="D6" t="n">
-        <v>1073</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>458</v>
+        <v>309</v>
       </c>
       <c r="C7" t="n">
-        <v>1451</v>
+        <v>1721</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>153</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>680</v>
+        <v>821</v>
       </c>
       <c r="D8" t="n">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2142,7 +2142,7 @@
         <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
+        <v>164</v>
+      </c>
+      <c r="D11" t="n">
         <v>167</v>
-      </c>
-      <c r="D11" t="n">
-        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2170,7 +2170,7 @@
         <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7837</v>
+        <v>5124</v>
       </c>
       <c r="C2" t="n">
-        <v>5637</v>
+        <v>4378</v>
       </c>
       <c r="D2" t="n">
-        <v>30432</v>
+        <v>22272</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6138</v>
+        <v>4653</v>
       </c>
       <c r="C3" t="n">
-        <v>3019</v>
+        <v>3768</v>
       </c>
       <c r="D3" t="n">
-        <v>17637</v>
+        <v>22608</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4685</v>
+        <v>3764</v>
       </c>
       <c r="C4" t="n">
-        <v>4725</v>
+        <v>6245</v>
       </c>
       <c r="D4" t="n">
-        <v>12427</v>
+        <v>13569</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2429</v>
+        <v>1971</v>
       </c>
       <c r="C5" t="n">
-        <v>4279</v>
+        <v>5992</v>
       </c>
       <c r="D5" t="n">
-        <v>5199</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1429</v>
+        <v>1076</v>
       </c>
       <c r="C6" t="n">
-        <v>2956</v>
+        <v>3962</v>
       </c>
       <c r="D6" t="n">
-        <v>1527</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>690</v>
+        <v>473</v>
       </c>
       <c r="C7" t="n">
-        <v>1888</v>
+        <v>2272</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>231</v>
+        <v>156</v>
       </c>
       <c r="C8" t="n">
-        <v>1011</v>
+        <v>1190</v>
       </c>
       <c r="D8" t="n">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>466</v>
+        <v>521</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4569</v>
+        <v>3053</v>
       </c>
       <c r="C2" t="n">
-        <v>2537</v>
+        <v>2063</v>
       </c>
       <c r="D2" t="n">
-        <v>20992</v>
+        <v>15586</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6388</v>
+        <v>4598</v>
       </c>
       <c r="C3" t="n">
-        <v>3839</v>
+        <v>3822</v>
       </c>
       <c r="D3" t="n">
-        <v>18646</v>
+        <v>22066</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5180</v>
+        <v>4126</v>
       </c>
       <c r="C4" t="n">
-        <v>4490</v>
+        <v>5942</v>
       </c>
       <c r="D4" t="n">
-        <v>13145</v>
+        <v>14638</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2553</v>
+        <v>2013</v>
       </c>
       <c r="C5" t="n">
-        <v>4954</v>
+        <v>6920</v>
       </c>
       <c r="D5" t="n">
-        <v>5617</v>
+        <v>5437</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1244</v>
+        <v>874</v>
       </c>
       <c r="C6" t="n">
-        <v>3693</v>
+        <v>4746</v>
       </c>
       <c r="D6" t="n">
-        <v>1487</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>213</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>1958</v>
+        <v>2307</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>783</v>
+        <v>883</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5603</v>
+        <v>3804</v>
       </c>
       <c r="C2" t="n">
-        <v>2154</v>
+        <v>6732</v>
       </c>
       <c r="D2" t="n">
-        <v>19777</v>
+        <v>16907</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4782</v>
+        <v>3391</v>
       </c>
       <c r="C3" t="n">
-        <v>2861</v>
+        <v>2696</v>
       </c>
       <c r="D3" t="n">
-        <v>17879</v>
+        <v>19701</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5011</v>
+        <v>3777</v>
       </c>
       <c r="C4" t="n">
-        <v>4077</v>
+        <v>4821</v>
       </c>
       <c r="D4" t="n">
-        <v>13643</v>
+        <v>15545</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3213</v>
+        <v>2530</v>
       </c>
       <c r="C5" t="n">
-        <v>4680</v>
+        <v>6401</v>
       </c>
       <c r="D5" t="n">
-        <v>6602</v>
+        <v>6596</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1594</v>
+        <v>1184</v>
       </c>
       <c r="C6" t="n">
-        <v>4250</v>
+        <v>5667</v>
       </c>
       <c r="D6" t="n">
-        <v>2076</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>484</v>
+        <v>321</v>
       </c>
       <c r="C7" t="n">
-        <v>2726</v>
+        <v>3331</v>
       </c>
       <c r="D7" t="n">
-        <v>705</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1247</v>
+        <v>1416</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" t="n">
         <v>61</v>
-      </c>
-      <c r="D13" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4302</v>
+        <v>2665</v>
       </c>
       <c r="C2" t="n">
-        <v>1489</v>
+        <v>4408</v>
       </c>
       <c r="D2" t="n">
-        <v>15221</v>
+        <v>12701</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4428</v>
+        <v>3087</v>
       </c>
       <c r="C3" t="n">
-        <v>2320</v>
+        <v>3898</v>
       </c>
       <c r="D3" t="n">
-        <v>17292</v>
+        <v>18293</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4548</v>
+        <v>3344</v>
       </c>
       <c r="C4" t="n">
-        <v>3584</v>
+        <v>3982</v>
       </c>
       <c r="D4" t="n">
-        <v>13928</v>
+        <v>15780</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3548</v>
+        <v>2773</v>
       </c>
       <c r="C5" t="n">
-        <v>4530</v>
+        <v>5937</v>
       </c>
       <c r="D5" t="n">
-        <v>7275</v>
+        <v>7553</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1915</v>
+        <v>1410</v>
       </c>
       <c r="C6" t="n">
-        <v>4568</v>
+        <v>6131</v>
       </c>
       <c r="D6" t="n">
-        <v>2546</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>472</v>
+        <v>300</v>
       </c>
       <c r="C7" t="n">
-        <v>3315</v>
+        <v>4130</v>
       </c>
       <c r="D7" t="n">
-        <v>807</v>
+        <v>817</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>1630</v>
+        <v>1858</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>137</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6361</v>
+        <v>4016</v>
       </c>
       <c r="C2" t="n">
-        <v>10939</v>
+        <v>10616</v>
       </c>
       <c r="D2" t="n">
-        <v>15040</v>
+        <v>15734</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3681</v>
+        <v>2472</v>
       </c>
       <c r="C3" t="n">
-        <v>1740</v>
+        <v>3645</v>
       </c>
       <c r="D3" t="n">
-        <v>15892</v>
+        <v>16451</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3913</v>
+        <v>2827</v>
       </c>
       <c r="C4" t="n">
-        <v>2939</v>
+        <v>3862</v>
       </c>
       <c r="D4" t="n">
-        <v>14021</v>
+        <v>15662</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3591</v>
+        <v>2736</v>
       </c>
       <c r="C5" t="n">
-        <v>4027</v>
+        <v>5006</v>
       </c>
       <c r="D5" t="n">
-        <v>8011</v>
+        <v>8429</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2320</v>
+        <v>1719</v>
       </c>
       <c r="C6" t="n">
-        <v>4511</v>
+        <v>6061</v>
       </c>
       <c r="D6" t="n">
-        <v>3148</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>849</v>
+        <v>585</v>
       </c>
       <c r="C7" t="n">
-        <v>3849</v>
+        <v>4873</v>
       </c>
       <c r="D7" t="n">
-        <v>1020</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>2256</v>
+        <v>2658</v>
       </c>
       <c r="D8" t="n">
-        <v>472</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>933</v>
+        <v>992</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
         <v>140</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9425</v>
+        <v>5655</v>
       </c>
       <c r="C2" t="n">
-        <v>3030</v>
+        <v>3495</v>
       </c>
       <c r="D2" t="n">
-        <v>12421</v>
+        <v>19834</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4458</v>
+        <v>2875</v>
       </c>
       <c r="C2" t="n">
-        <v>6038</v>
+        <v>6029</v>
       </c>
       <c r="D2" t="n">
-        <v>10950</v>
+        <v>11581</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4964</v>
+        <v>3350</v>
       </c>
       <c r="C3" t="n">
-        <v>4166</v>
+        <v>5577</v>
       </c>
       <c r="D3" t="n">
-        <v>17146</v>
+        <v>17852</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5319</v>
+        <v>3969</v>
       </c>
       <c r="C4" t="n">
-        <v>4198</v>
+        <v>5630</v>
       </c>
       <c r="D4" t="n">
-        <v>14498</v>
+        <v>15925</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2309</v>
+        <v>1664</v>
       </c>
       <c r="C5" t="n">
-        <v>6110</v>
+        <v>8019</v>
       </c>
       <c r="D5" t="n">
-        <v>7356</v>
+        <v>7607</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>784</v>
+        <v>540</v>
       </c>
       <c r="C6" t="n">
-        <v>4788</v>
+        <v>5963</v>
       </c>
       <c r="D6" t="n">
-        <v>2433</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>2210</v>
+        <v>2604</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>914</v>
+        <v>972</v>
       </c>
       <c r="D8" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>137</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8330</v>
+        <v>5889</v>
       </c>
       <c r="C2" t="n">
-        <v>2391</v>
+        <v>4503</v>
       </c>
       <c r="D2" t="n">
-        <v>17264</v>
+        <v>19812</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4001</v>
+        <v>2403</v>
       </c>
       <c r="C3" t="n">
-        <v>1527</v>
+        <v>1761</v>
       </c>
       <c r="D3" t="n">
-        <v>2726</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6343</v>
+        <v>4131</v>
       </c>
       <c r="C2" t="n">
-        <v>5696</v>
+        <v>7107</v>
       </c>
       <c r="D2" t="n">
-        <v>21591</v>
+        <v>21240</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5068</v>
+        <v>3405</v>
       </c>
       <c r="C3" t="n">
-        <v>1738</v>
+        <v>2856</v>
       </c>
       <c r="D3" t="n">
-        <v>4967</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1772</v>
+        <v>1078</v>
       </c>
       <c r="C4" t="n">
-        <v>939</v>
+        <v>1076</v>
       </c>
       <c r="D4" t="n">
-        <v>1730</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4896,7 +4896,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7653</v>
+        <v>6141</v>
       </c>
       <c r="C2" t="n">
-        <v>7218</v>
+        <v>6084</v>
       </c>
       <c r="D2" t="n">
-        <v>33994</v>
+        <v>31484</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4688</v>
+        <v>3098</v>
       </c>
       <c r="C3" t="n">
-        <v>3372</v>
+        <v>4478</v>
       </c>
       <c r="D3" t="n">
-        <v>7269</v>
+        <v>8267</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2900</v>
+        <v>1899</v>
       </c>
       <c r="C4" t="n">
-        <v>1372</v>
+        <v>2061</v>
       </c>
       <c r="D4" t="n">
-        <v>2298</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>787</v>
+        <v>503</v>
       </c>
       <c r="C5" t="n">
-        <v>609</v>
+        <v>682</v>
       </c>
       <c r="D5" t="n">
-        <v>1237</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
         <v>915</v>
@@ -5207,7 +5207,7 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
         <v>622</v>
@@ -5221,7 +5221,7 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
         <v>460</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7256</v>
+        <v>7074</v>
       </c>
       <c r="C2" t="n">
-        <v>4511</v>
+        <v>7129</v>
       </c>
       <c r="D2" t="n">
-        <v>36075</v>
+        <v>28091</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4994</v>
+        <v>3707</v>
       </c>
       <c r="C3" t="n">
-        <v>4657</v>
+        <v>4617</v>
       </c>
       <c r="D3" t="n">
-        <v>10819</v>
+        <v>11213</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3236</v>
+        <v>2130</v>
       </c>
       <c r="C4" t="n">
-        <v>2418</v>
+        <v>3297</v>
       </c>
       <c r="D4" t="n">
-        <v>3134</v>
+        <v>3678</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1519</v>
+        <v>988</v>
       </c>
       <c r="C5" t="n">
-        <v>986</v>
+        <v>1395</v>
       </c>
       <c r="D5" t="n">
-        <v>1370</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>398</v>
+        <v>283</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>492</v>
       </c>
       <c r="D6" t="n">
-        <v>958</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
         <v>658</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
         <v>482</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
         <v>377</v>
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5574,7 +5574,7 @@
         <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8298</v>
+        <v>7214</v>
       </c>
       <c r="C2" t="n">
-        <v>5250</v>
+        <v>7293</v>
       </c>
       <c r="D2" t="n">
-        <v>35532</v>
+        <v>32522</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4432</v>
+        <v>3872</v>
       </c>
       <c r="C3" t="n">
-        <v>3754</v>
+        <v>4833</v>
       </c>
       <c r="D3" t="n">
-        <v>13073</v>
+        <v>12220</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2536</v>
+        <v>1797</v>
       </c>
       <c r="C4" t="n">
-        <v>2973</v>
+        <v>3272</v>
       </c>
       <c r="D4" t="n">
-        <v>3876</v>
+        <v>4281</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1251</v>
+        <v>814</v>
       </c>
       <c r="C5" t="n">
-        <v>1276</v>
+        <v>1757</v>
       </c>
       <c r="D5" t="n">
-        <v>1312</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>449</v>
+        <v>304</v>
       </c>
       <c r="C6" t="n">
-        <v>486</v>
+        <v>634</v>
       </c>
       <c r="D6" t="n">
-        <v>782</v>
+        <v>802</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
         <v>194</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6928</v>
+        <v>6579</v>
       </c>
       <c r="C2" t="n">
-        <v>3668</v>
+        <v>9049</v>
       </c>
       <c r="D2" t="n">
-        <v>29678</v>
+        <v>32564</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5293</v>
+        <v>4609</v>
       </c>
       <c r="C3" t="n">
-        <v>3985</v>
+        <v>5404</v>
       </c>
       <c r="D3" t="n">
-        <v>16042</v>
+        <v>14991</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3060</v>
+        <v>2498</v>
       </c>
       <c r="C4" t="n">
-        <v>3391</v>
+        <v>4163</v>
       </c>
       <c r="D4" t="n">
-        <v>5700</v>
+        <v>5710</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1679</v>
+        <v>1156</v>
       </c>
       <c r="C5" t="n">
-        <v>2259</v>
+        <v>2622</v>
       </c>
       <c r="D5" t="n">
-        <v>1789</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>793</v>
+        <v>522</v>
       </c>
       <c r="C6" t="n">
-        <v>935</v>
+        <v>1272</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>256</v>
+        <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>386</v>
+        <v>476</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="D8" t="n">
         <v>386</v>
@@ -6182,7 +6182,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6602</v>
+        <v>6087</v>
       </c>
       <c r="C2" t="n">
-        <v>3498</v>
+        <v>4090</v>
       </c>
       <c r="D2" t="n">
-        <v>25513</v>
+        <v>26862</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5071</v>
+        <v>4581</v>
       </c>
       <c r="C3" t="n">
-        <v>3299</v>
+        <v>6398</v>
       </c>
       <c r="D3" t="n">
-        <v>17068</v>
+        <v>16723</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3565</v>
+        <v>3030</v>
       </c>
       <c r="C4" t="n">
-        <v>3624</v>
+        <v>4779</v>
       </c>
       <c r="D4" t="n">
-        <v>7512</v>
+        <v>7318</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2089</v>
+        <v>1598</v>
       </c>
       <c r="C5" t="n">
-        <v>2842</v>
+        <v>3385</v>
       </c>
       <c r="D5" t="n">
-        <v>2430</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1116</v>
+        <v>756</v>
       </c>
       <c r="C6" t="n">
-        <v>1635</v>
+        <v>1983</v>
       </c>
       <c r="D6" t="n">
-        <v>1020</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>464</v>
+        <v>312</v>
       </c>
       <c r="C7" t="n">
-        <v>676</v>
+        <v>897</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>312</v>
+        <v>364</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D9" t="n">
         <v>294</v>
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>155</v>
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">

--- a/output/yearly_population_iteration_87_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_87_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8254</v>
+        <v>1361</v>
       </c>
       <c r="C2" t="n">
-        <v>7015</v>
+        <v>2279</v>
       </c>
       <c r="D2" t="n">
-        <v>38903</v>
+        <v>15091</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4386</v>
+        <v>2331</v>
       </c>
       <c r="C3" t="n">
-        <v>4563</v>
+        <v>4601</v>
       </c>
       <c r="D3" t="n">
-        <v>17086</v>
+        <v>13027</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3202</v>
+        <v>1588</v>
       </c>
       <c r="C4" t="n">
-        <v>5534</v>
+        <v>5816</v>
       </c>
       <c r="D4" t="n">
-        <v>8811</v>
+        <v>5803</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1977</v>
+        <v>843</v>
       </c>
       <c r="C5" t="n">
-        <v>4023</v>
+        <v>3309</v>
       </c>
       <c r="D5" t="n">
-        <v>3337</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1047</v>
+        <v>353</v>
       </c>
       <c r="C6" t="n">
-        <v>2628</v>
+        <v>1348</v>
       </c>
       <c r="D6" t="n">
-        <v>1320</v>
+        <v>758</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>459</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>1428</v>
+        <v>599</v>
       </c>
       <c r="D7" t="n">
-        <v>689</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>177</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>614</v>
+        <v>345</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7985</v>
+        <v>1065</v>
       </c>
       <c r="C2" t="n">
-        <v>4939</v>
+        <v>2718</v>
       </c>
       <c r="D2" t="n">
-        <v>47517</v>
+        <v>17428</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4940</v>
+        <v>1566</v>
       </c>
       <c r="C3" t="n">
-        <v>4996</v>
+        <v>2904</v>
       </c>
       <c r="D3" t="n">
-        <v>18904</v>
+        <v>12419</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3206</v>
+        <v>1697</v>
       </c>
       <c r="C4" t="n">
-        <v>4952</v>
+        <v>5006</v>
       </c>
       <c r="D4" t="n">
-        <v>9893</v>
+        <v>7013</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2205</v>
+        <v>1060</v>
       </c>
       <c r="C5" t="n">
-        <v>4596</v>
+        <v>4643</v>
       </c>
       <c r="D5" t="n">
-        <v>4044</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1312</v>
+        <v>529</v>
       </c>
       <c r="C6" t="n">
-        <v>3231</v>
+        <v>2362</v>
       </c>
       <c r="D6" t="n">
-        <v>1612</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>639</v>
+        <v>191</v>
       </c>
       <c r="C7" t="n">
-        <v>1942</v>
+        <v>978</v>
       </c>
       <c r="D7" t="n">
-        <v>767</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>964</v>
+        <v>471</v>
       </c>
       <c r="D8" t="n">
-        <v>468</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>418</v>
+        <v>318</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8827</v>
+        <v>558</v>
       </c>
       <c r="C2" t="n">
-        <v>7327</v>
+        <v>1106</v>
       </c>
       <c r="D2" t="n">
-        <v>46954</v>
+        <v>11759</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5036</v>
+        <v>1360</v>
       </c>
       <c r="C3" t="n">
-        <v>4415</v>
+        <v>2698</v>
       </c>
       <c r="D3" t="n">
-        <v>21127</v>
+        <v>12722</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3320</v>
+        <v>1853</v>
       </c>
       <c r="C4" t="n">
-        <v>4820</v>
+        <v>4514</v>
       </c>
       <c r="D4" t="n">
-        <v>10794</v>
+        <v>7759</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2334</v>
+        <v>1091</v>
       </c>
       <c r="C5" t="n">
-        <v>4606</v>
+        <v>5323</v>
       </c>
       <c r="D5" t="n">
-        <v>4724</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1513</v>
+        <v>422</v>
       </c>
       <c r="C6" t="n">
-        <v>3765</v>
+        <v>3178</v>
       </c>
       <c r="D6" t="n">
-        <v>1940</v>
+        <v>973</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>807</v>
+        <v>79</v>
       </c>
       <c r="C7" t="n">
-        <v>2440</v>
+        <v>1005</v>
       </c>
       <c r="D7" t="n">
-        <v>867</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>356</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1337</v>
+        <v>487</v>
       </c>
       <c r="D8" t="n">
-        <v>504</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>626</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>300</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>199</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8187</v>
+        <v>755</v>
       </c>
       <c r="C2" t="n">
-        <v>4982</v>
+        <v>2927</v>
       </c>
       <c r="D2" t="n">
-        <v>38577</v>
+        <v>10849</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6003</v>
+        <v>839</v>
       </c>
       <c r="C3" t="n">
-        <v>7107</v>
+        <v>1609</v>
       </c>
       <c r="D3" t="n">
-        <v>22583</v>
+        <v>11774</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2156</v>
+        <v>1432</v>
       </c>
       <c r="C4" t="n">
-        <v>7059</v>
+        <v>3452</v>
       </c>
       <c r="D4" t="n">
-        <v>10311</v>
+        <v>8428</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1398</v>
+        <v>1303</v>
       </c>
       <c r="C5" t="n">
-        <v>3689</v>
+        <v>4836</v>
       </c>
       <c r="D5" t="n">
-        <v>3171</v>
+        <v>3695</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>745</v>
+        <v>644</v>
       </c>
       <c r="C6" t="n">
-        <v>2391</v>
+        <v>4276</v>
       </c>
       <c r="D6" t="n">
-        <v>849</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>328</v>
+        <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>1310</v>
+        <v>2046</v>
       </c>
       <c r="D7" t="n">
-        <v>493</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>613</v>
+        <v>724</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4915</v>
+        <v>540</v>
       </c>
       <c r="C2" t="n">
-        <v>2705</v>
+        <v>2410</v>
       </c>
       <c r="D2" t="n">
-        <v>27205</v>
+        <v>7940</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5995</v>
+        <v>702</v>
       </c>
       <c r="C3" t="n">
-        <v>5620</v>
+        <v>2005</v>
       </c>
       <c r="D3" t="n">
-        <v>23457</v>
+        <v>10943</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3116</v>
+        <v>1125</v>
       </c>
       <c r="C4" t="n">
-        <v>7137</v>
+        <v>2559</v>
       </c>
       <c r="D4" t="n">
-        <v>12080</v>
+        <v>8798</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1583</v>
+        <v>1329</v>
       </c>
       <c r="C5" t="n">
-        <v>5180</v>
+        <v>4296</v>
       </c>
       <c r="D5" t="n">
-        <v>4026</v>
+        <v>4335</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>889</v>
+        <v>795</v>
       </c>
       <c r="C6" t="n">
-        <v>2962</v>
+        <v>4711</v>
       </c>
       <c r="D6" t="n">
-        <v>1086</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>217</v>
       </c>
       <c r="C7" t="n">
-        <v>1721</v>
+        <v>2906</v>
       </c>
       <c r="D7" t="n">
-        <v>540</v>
+        <v>685</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>821</v>
+        <v>1105</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>339</v>
+        <v>453</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5124</v>
+        <v>929</v>
       </c>
       <c r="C2" t="n">
-        <v>4378</v>
+        <v>7464</v>
       </c>
       <c r="D2" t="n">
-        <v>22272</v>
+        <v>11194</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4653</v>
+        <v>529</v>
       </c>
       <c r="C3" t="n">
-        <v>3768</v>
+        <v>1945</v>
       </c>
       <c r="D3" t="n">
-        <v>22608</v>
+        <v>9757</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3764</v>
+        <v>828</v>
       </c>
       <c r="C4" t="n">
-        <v>6245</v>
+        <v>2218</v>
       </c>
       <c r="D4" t="n">
-        <v>13569</v>
+        <v>8901</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1971</v>
+        <v>1142</v>
       </c>
       <c r="C5" t="n">
-        <v>5992</v>
+        <v>3380</v>
       </c>
       <c r="D5" t="n">
-        <v>5140</v>
+        <v>4931</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1076</v>
+        <v>949</v>
       </c>
       <c r="C6" t="n">
-        <v>3962</v>
+        <v>4467</v>
       </c>
       <c r="D6" t="n">
-        <v>1495</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>473</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>2272</v>
+        <v>3764</v>
       </c>
       <c r="D7" t="n">
-        <v>609</v>
+        <v>811</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>1190</v>
+        <v>1891</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>518</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
-        <v>521</v>
+        <v>719</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>262</v>
+        <v>321</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3053</v>
+        <v>601</v>
       </c>
       <c r="C2" t="n">
-        <v>2063</v>
+        <v>3642</v>
       </c>
       <c r="D2" t="n">
-        <v>15586</v>
+        <v>7970</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4598</v>
+        <v>796</v>
       </c>
       <c r="C3" t="n">
-        <v>3822</v>
+        <v>3803</v>
       </c>
       <c r="D3" t="n">
-        <v>22066</v>
+        <v>10506</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4126</v>
+        <v>1440</v>
       </c>
       <c r="C4" t="n">
-        <v>5942</v>
+        <v>3267</v>
       </c>
       <c r="D4" t="n">
-        <v>14638</v>
+        <v>9384</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2013</v>
+        <v>992</v>
       </c>
       <c r="C5" t="n">
-        <v>6920</v>
+        <v>5606</v>
       </c>
       <c r="D5" t="n">
-        <v>5437</v>
+        <v>4656</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>874</v>
+        <v>369</v>
       </c>
       <c r="C6" t="n">
-        <v>4746</v>
+        <v>4958</v>
       </c>
       <c r="D6" t="n">
-        <v>1453</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>2307</v>
+        <v>1853</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>883</v>
+        <v>704</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>256</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3804</v>
+        <v>375</v>
       </c>
       <c r="C2" t="n">
-        <v>6732</v>
+        <v>1898</v>
       </c>
       <c r="D2" t="n">
-        <v>16907</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3391</v>
+        <v>596</v>
       </c>
       <c r="C3" t="n">
-        <v>2696</v>
+        <v>3289</v>
       </c>
       <c r="D3" t="n">
-        <v>19701</v>
+        <v>9352</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3777</v>
+        <v>945</v>
       </c>
       <c r="C4" t="n">
-        <v>4821</v>
+        <v>3354</v>
       </c>
       <c r="D4" t="n">
-        <v>15545</v>
+        <v>8928</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2530</v>
+        <v>875</v>
       </c>
       <c r="C5" t="n">
-        <v>6401</v>
+        <v>3938</v>
       </c>
       <c r="D5" t="n">
-        <v>6596</v>
+        <v>4809</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1184</v>
+        <v>377</v>
       </c>
       <c r="C6" t="n">
-        <v>5667</v>
+        <v>4392</v>
       </c>
       <c r="D6" t="n">
-        <v>1969</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>321</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>3331</v>
+        <v>2382</v>
       </c>
       <c r="D7" t="n">
-        <v>711</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1416</v>
+        <v>791</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>466</v>
+        <v>290</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>143</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2665</v>
+        <v>479</v>
       </c>
       <c r="C2" t="n">
-        <v>4408</v>
+        <v>4107</v>
       </c>
       <c r="D2" t="n">
-        <v>12701</v>
+        <v>12174</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3087</v>
+        <v>404</v>
       </c>
       <c r="C3" t="n">
-        <v>3898</v>
+        <v>2156</v>
       </c>
       <c r="D3" t="n">
-        <v>18293</v>
+        <v>8133</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3344</v>
+        <v>677</v>
       </c>
       <c r="C4" t="n">
-        <v>3982</v>
+        <v>3245</v>
       </c>
       <c r="D4" t="n">
-        <v>15780</v>
+        <v>8742</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2773</v>
+        <v>831</v>
       </c>
       <c r="C5" t="n">
-        <v>5937</v>
+        <v>3557</v>
       </c>
       <c r="D5" t="n">
-        <v>7553</v>
+        <v>5453</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1410</v>
+        <v>565</v>
       </c>
       <c r="C6" t="n">
-        <v>6131</v>
+        <v>4134</v>
       </c>
       <c r="D6" t="n">
-        <v>2383</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>194</v>
       </c>
       <c r="C7" t="n">
-        <v>4130</v>
+        <v>3468</v>
       </c>
       <c r="D7" t="n">
-        <v>817</v>
+        <v>833</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n">
-        <v>1858</v>
+        <v>1593</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>552</v>
+        <v>528</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4016</v>
+        <v>601</v>
       </c>
       <c r="C2" t="n">
-        <v>10616</v>
+        <v>6432</v>
       </c>
       <c r="D2" t="n">
-        <v>15734</v>
+        <v>13428</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2472</v>
+        <v>362</v>
       </c>
       <c r="C3" t="n">
-        <v>3645</v>
+        <v>2774</v>
       </c>
       <c r="D3" t="n">
-        <v>16451</v>
+        <v>8193</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2827</v>
+        <v>476</v>
       </c>
       <c r="C4" t="n">
-        <v>3862</v>
+        <v>2571</v>
       </c>
       <c r="D4" t="n">
-        <v>15662</v>
+        <v>8359</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2736</v>
+        <v>695</v>
       </c>
       <c r="C5" t="n">
-        <v>5006</v>
+        <v>3315</v>
       </c>
       <c r="D5" t="n">
-        <v>8429</v>
+        <v>5887</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1719</v>
+        <v>640</v>
       </c>
       <c r="C6" t="n">
-        <v>6061</v>
+        <v>3788</v>
       </c>
       <c r="D6" t="n">
-        <v>2974</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>585</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>4873</v>
+        <v>3806</v>
       </c>
       <c r="D7" t="n">
-        <v>1008</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>2658</v>
+        <v>2511</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>992</v>
+        <v>1028</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5655</v>
+        <v>5154</v>
       </c>
       <c r="C2" t="n">
-        <v>3495</v>
+        <v>7306</v>
       </c>
       <c r="D2" t="n">
-        <v>19834</v>
+        <v>14375</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2875</v>
+        <v>1393</v>
       </c>
       <c r="C2" t="n">
-        <v>6029</v>
+        <v>9398</v>
       </c>
       <c r="D2" t="n">
-        <v>11581</v>
+        <v>15399</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3350</v>
+        <v>384</v>
       </c>
       <c r="C3" t="n">
-        <v>5577</v>
+        <v>3978</v>
       </c>
       <c r="D3" t="n">
-        <v>17852</v>
+        <v>8383</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3969</v>
+        <v>366</v>
       </c>
       <c r="C4" t="n">
-        <v>5630</v>
+        <v>2620</v>
       </c>
       <c r="D4" t="n">
-        <v>15925</v>
+        <v>8076</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1664</v>
+        <v>553</v>
       </c>
       <c r="C5" t="n">
-        <v>8019</v>
+        <v>2849</v>
       </c>
       <c r="D5" t="n">
-        <v>7607</v>
+        <v>6054</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>540</v>
+        <v>624</v>
       </c>
       <c r="C6" t="n">
-        <v>5963</v>
+        <v>3521</v>
       </c>
       <c r="D6" t="n">
-        <v>2316</v>
+        <v>3317</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>417</v>
       </c>
       <c r="C7" t="n">
-        <v>2604</v>
+        <v>3796</v>
       </c>
       <c r="D7" t="n">
-        <v>577</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="C8" t="n">
-        <v>972</v>
+        <v>3093</v>
       </c>
       <c r="D8" t="n">
-        <v>299</v>
+        <v>539</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>1667</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>627</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>231</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5889</v>
+        <v>6412</v>
       </c>
       <c r="C2" t="n">
-        <v>4503</v>
+        <v>4846</v>
       </c>
       <c r="D2" t="n">
-        <v>19812</v>
+        <v>12527</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2403</v>
+        <v>1702</v>
       </c>
       <c r="C3" t="n">
-        <v>1761</v>
+        <v>2885</v>
       </c>
       <c r="D3" t="n">
-        <v>3971</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4131</v>
+        <v>2925</v>
       </c>
       <c r="C2" t="n">
-        <v>7107</v>
+        <v>3278</v>
       </c>
       <c r="D2" t="n">
-        <v>21240</v>
+        <v>20273</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3405</v>
+        <v>3437</v>
       </c>
       <c r="C3" t="n">
-        <v>2856</v>
+        <v>3489</v>
       </c>
       <c r="D3" t="n">
-        <v>6340</v>
+        <v>4131</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1078</v>
+        <v>812</v>
       </c>
       <c r="C4" t="n">
-        <v>1076</v>
+        <v>1847</v>
       </c>
       <c r="D4" t="n">
-        <v>1981</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6141</v>
+        <v>2204</v>
       </c>
       <c r="C2" t="n">
-        <v>6084</v>
+        <v>5146</v>
       </c>
       <c r="D2" t="n">
-        <v>31484</v>
+        <v>23472</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3098</v>
+        <v>2622</v>
       </c>
       <c r="C3" t="n">
-        <v>4478</v>
+        <v>2891</v>
       </c>
       <c r="D3" t="n">
-        <v>8267</v>
+        <v>6538</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1899</v>
+        <v>1868</v>
       </c>
       <c r="C4" t="n">
-        <v>2061</v>
+        <v>2801</v>
       </c>
       <c r="D4" t="n">
-        <v>2757</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>503</v>
+        <v>392</v>
       </c>
       <c r="C5" t="n">
-        <v>682</v>
+        <v>1162</v>
       </c>
       <c r="D5" t="n">
-        <v>1283</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>218</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7074</v>
+        <v>2486</v>
       </c>
       <c r="C2" t="n">
-        <v>7129</v>
+        <v>5503</v>
       </c>
       <c r="D2" t="n">
-        <v>28091</v>
+        <v>21668</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3707</v>
+        <v>1998</v>
       </c>
       <c r="C3" t="n">
-        <v>4617</v>
+        <v>3580</v>
       </c>
       <c r="D3" t="n">
-        <v>11213</v>
+        <v>8776</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2130</v>
+        <v>1944</v>
       </c>
       <c r="C4" t="n">
-        <v>3297</v>
+        <v>2794</v>
       </c>
       <c r="D4" t="n">
-        <v>3678</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>988</v>
+        <v>955</v>
       </c>
       <c r="C5" t="n">
-        <v>1395</v>
+        <v>2050</v>
       </c>
       <c r="D5" t="n">
-        <v>1486</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>283</v>
+        <v>226</v>
       </c>
       <c r="C6" t="n">
-        <v>492</v>
+        <v>741</v>
       </c>
       <c r="D6" t="n">
-        <v>965</v>
+        <v>847</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7214</v>
+        <v>2521</v>
       </c>
       <c r="C2" t="n">
-        <v>7293</v>
+        <v>5832</v>
       </c>
       <c r="D2" t="n">
-        <v>32522</v>
+        <v>19607</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3872</v>
+        <v>1839</v>
       </c>
       <c r="C3" t="n">
-        <v>4833</v>
+        <v>3987</v>
       </c>
       <c r="D3" t="n">
-        <v>12220</v>
+        <v>10117</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1797</v>
+        <v>1711</v>
       </c>
       <c r="C4" t="n">
-        <v>3272</v>
+        <v>3165</v>
       </c>
       <c r="D4" t="n">
-        <v>4281</v>
+        <v>3816</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>814</v>
+        <v>1247</v>
       </c>
       <c r="C5" t="n">
-        <v>1757</v>
+        <v>2380</v>
       </c>
       <c r="D5" t="n">
-        <v>1492</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>304</v>
+        <v>516</v>
       </c>
       <c r="C6" t="n">
-        <v>634</v>
+        <v>1411</v>
       </c>
       <c r="D6" t="n">
-        <v>802</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>270</v>
+        <v>521</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6579</v>
+        <v>3179</v>
       </c>
       <c r="C2" t="n">
-        <v>9049</v>
+        <v>6438</v>
       </c>
       <c r="D2" t="n">
-        <v>32564</v>
+        <v>28767</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4609</v>
+        <v>1769</v>
       </c>
       <c r="C3" t="n">
-        <v>5404</v>
+        <v>4280</v>
       </c>
       <c r="D3" t="n">
-        <v>14991</v>
+        <v>10787</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2498</v>
+        <v>1521</v>
       </c>
       <c r="C4" t="n">
-        <v>4163</v>
+        <v>3494</v>
       </c>
       <c r="D4" t="n">
-        <v>5710</v>
+        <v>4752</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1156</v>
+        <v>1309</v>
       </c>
       <c r="C5" t="n">
-        <v>2622</v>
+        <v>2729</v>
       </c>
       <c r="D5" t="n">
-        <v>2008</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>522</v>
+        <v>765</v>
       </c>
       <c r="C6" t="n">
-        <v>1272</v>
+        <v>1870</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>980</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>181</v>
+        <v>278</v>
       </c>
       <c r="C7" t="n">
-        <v>476</v>
+        <v>948</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>248</v>
+        <v>399</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6087</v>
+        <v>2799</v>
       </c>
       <c r="C2" t="n">
-        <v>4090</v>
+        <v>3862</v>
       </c>
       <c r="D2" t="n">
-        <v>26862</v>
+        <v>22426</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4581</v>
+        <v>2546</v>
       </c>
       <c r="C3" t="n">
-        <v>6398</v>
+        <v>6503</v>
       </c>
       <c r="D3" t="n">
-        <v>16723</v>
+        <v>12219</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3030</v>
+        <v>1209</v>
       </c>
       <c r="C4" t="n">
-        <v>4779</v>
+        <v>4867</v>
       </c>
       <c r="D4" t="n">
-        <v>7318</v>
+        <v>4524</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1598</v>
+        <v>706</v>
       </c>
       <c r="C5" t="n">
-        <v>3385</v>
+        <v>1832</v>
       </c>
       <c r="D5" t="n">
-        <v>2602</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>756</v>
+        <v>256</v>
       </c>
       <c r="C6" t="n">
-        <v>1983</v>
+        <v>929</v>
       </c>
       <c r="D6" t="n">
-        <v>1101</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>312</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>897</v>
+        <v>391</v>
       </c>
       <c r="D7" t="n">
-        <v>615</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>364</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>150</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
